--- a/data/handicaps.xlsx
+++ b/data/handicaps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{5632236C-9D87-4A4C-B74C-89F5347CD06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{131DC9CA-9674-4C14-90D0-75A3D75B4E3A}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{5632236C-9D87-4A4C-B74C-89F5347CD06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{463BD7E1-067B-4D19-B53C-5385DBA743C9}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="4575" windowWidth="15450" windowHeight="8460" xr2:uid="{945203A6-6E8C-40FC-9025-42874A8E7A61}"/>
+    <workbookView xWindow="11625" yWindow="5955" windowWidth="13005" windowHeight="8745" xr2:uid="{945203A6-6E8C-40FC-9025-42874A8E7A61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ダブルX:一つ被りが出るごとに、追加で1枚自分でXをつける</t>
   </si>
@@ -58,47 +58,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>時間短縮:制限時間が1分になった時点で回答をやめる</t>
-    <rPh sb="16" eb="18">
-      <t>ジテン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>カイトウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>回答被り:回答が被った人物はこのカードを持つ人の回答にNGを押す</t>
-    <rPh sb="0" eb="2">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カブ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カブ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ジンブツ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>同頭文字禁止:同じ頭文字から始まる回答は1つしか使えない。書くのは可能。例.ルフィ、ルッチと書くのは可能だが回答として使えるのは1つ（○○から始まる言葉の場合は2文字目が重複不可）</t>
     <rPh sb="71" eb="72">
       <t>ハジ</t>
@@ -117,6 +76,407 @@
     </rPh>
     <rPh sb="87" eb="89">
       <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正確性：回答に1つでもNGをつけられた場合、その後の回答は全てなかったものとされる。（全てカードを公開するが被り処理は行わず他プレイヤーは全回答にNGをつける）</t>
+    <rPh sb="0" eb="3">
+      <t>セイカクセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="69" eb="72">
+      <t>ゼンカイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回答被り:回答が被った人物はこのカードを持つ人の回答にNGを押す。自分の被りカードは消さなくてよい</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジンブツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間短縮:制限時間が半分になった時点で回答をやめる</t>
+    <rPh sb="10" eb="12">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジテン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トップバッター禁止：このカードを持つプレイヤーが回答フェーズで最初に回答する事になった場合、他プレイヤーは全てNGを押す。被り処理は行わない</t>
+    <rPh sb="7" eb="9">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンカー禁止：このカードを持つプレイヤーが回答フェーズで最後に回答する事になった場合、他プレイヤーは全てNGを押す。被り処理は行わない</t>
+    <rPh sb="4" eb="6">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>偶数限定：回答する文字数は偶数限定とする（・など含む）</t>
+    <rPh sb="0" eb="2">
+      <t>グウスウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>グウスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奇数限定：回答する文字数は奇数限定とする（・など含む）</t>
+    <rPh sb="0" eb="4">
+      <t>キスウゲンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数制限：7文字以上の回答は禁止</t>
+    <rPh sb="0" eb="5">
+      <t>モジスウセイゲン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>モジイジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数制限2：5文字以下の回答は禁止</t>
+    <rPh sb="0" eb="5">
+      <t>モジスウセイゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宣言増加：直前に宣言した数より2以上多く宣言する</t>
+    <rPh sb="0" eb="4">
+      <t>センゲンゾウカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宣言固定：直前に宣言した数と同じ数宣言する</t>
+    <rPh sb="0" eb="2">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字禁止：「ん」が含まれる回答は禁止　（漢字の読み方なども）</t>
+    <rPh sb="0" eb="4">
+      <t>モジキンシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字禁止2：「ー」が含まれる回答は禁止　（漢字の読み方なども）</t>
+    <rPh sb="0" eb="4">
+      <t>モジキンシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メジャー縛り：誰とも被らなかった回答はNGとする</t>
+    <rPh sb="4" eb="5">
+      <t>シバ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宣言縛り：次の宣言は1か10とする</t>
+    <rPh sb="0" eb="2">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シバ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回答制限：回答として使用できるものは濁点・半濁点が含まれる回答のみ</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ハンダクテン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字禁止3：濁点・半濁点が含まれる回答は禁止</t>
+    <rPh sb="0" eb="4">
+      <t>モジキンシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ハンダクテン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キンシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -142,7 +502,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="游明朝"/>
       <family val="1"/>
@@ -171,8 +531,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -496,35 +859,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50D47E1-9333-4B12-83F6-86BC52390A9D}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="80.25" customWidth="1"/>
+    <col min="1" max="1" width="80.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="33" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="34.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
